--- a/AAII_Financials/Quarterly/VMCA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VMCA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>VMCA</t>
   </si>
@@ -1071,8 +1071,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>200</v>
       </c>
       <c r="E17" s="3">
         <v>400</v>
@@ -1309,8 +1309,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>600</v>
       </c>
       <c r="E23" s="3">
         <v>1600</v>
@@ -1441,8 +1441,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>600</v>
       </c>
       <c r="E26" s="3">
         <v>1600</v>
@@ -1485,8 +1485,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>600</v>
       </c>
       <c r="E27" s="3">
         <v>1600</v>
@@ -1749,8 +1749,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>600</v>
       </c>
       <c r="E33" s="3">
         <v>1600</v>
@@ -1837,8 +1837,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>600</v>
       </c>
       <c r="E35" s="3">
         <v>1600</v>
@@ -2663,7 +2663,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>1500</v>
       </c>
       <c r="E58" s="3">
         <v>600</v>
@@ -3428,8 +3428,8 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
+      <c r="D76" s="3">
+        <v>56600</v>
       </c>
       <c r="E76" s="3">
         <v>56000</v>
@@ -3565,8 +3565,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>600</v>
       </c>
       <c r="E81" s="3">
         <v>1600</v>

--- a/AAII_Financials/Quarterly/VMCA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VMCA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>VMCA</t>
   </si>
@@ -656,63 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -725,8 +726,14 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -769,8 +776,14 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -813,8 +826,14 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -857,8 +876,14 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +900,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,8 +946,14 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,8 +996,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1007,8 +1046,14 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1051,8 +1096,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1066,38 +1117,40 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>100</v>
+      </c>
+      <c r="F17" s="3">
         <v>200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>100</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1110,8 +1163,14 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1119,29 +1178,29 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G18" s="3">
         <v>-400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1154,8 +1213,14 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1172,8 +1237,10 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1181,28 +1248,28 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>900</v>
+      </c>
+      <c r="F20" s="3">
+        <v>900</v>
+      </c>
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>2400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1216,8 +1283,14 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1225,17 +1298,17 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>600</v>
+      </c>
+      <c r="G21" s="3">
         <v>1600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1800</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1260,8 +1333,14 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1304,8 +1383,14 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1313,29 +1398,29 @@
         <v>600</v>
       </c>
       <c r="E23" s="3">
+        <v>800</v>
+      </c>
+      <c r="F23" s="3">
+        <v>600</v>
+      </c>
+      <c r="G23" s="3">
         <v>1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-100</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1348,8 +1433,14 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1392,8 +1483,14 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1436,8 +1533,14 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1445,29 +1548,29 @@
         <v>600</v>
       </c>
       <c r="E26" s="3">
+        <v>800</v>
+      </c>
+      <c r="F26" s="3">
+        <v>600</v>
+      </c>
+      <c r="G26" s="3">
         <v>1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1480,8 +1583,14 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1489,29 +1598,29 @@
         <v>600</v>
       </c>
       <c r="E27" s="3">
+        <v>800</v>
+      </c>
+      <c r="F27" s="3">
+        <v>600</v>
+      </c>
+      <c r="G27" s="3">
         <v>1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1524,8 +1633,14 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1568,8 +1683,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1612,8 +1733,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1656,8 +1783,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1700,8 +1833,14 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1709,28 +1848,28 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-2400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1744,8 +1883,14 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1753,29 +1898,29 @@
         <v>600</v>
       </c>
       <c r="E33" s="3">
+        <v>800</v>
+      </c>
+      <c r="F33" s="3">
+        <v>600</v>
+      </c>
+      <c r="G33" s="3">
         <v>1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1788,8 +1933,14 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1832,8 +1983,14 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1841,29 +1998,29 @@
         <v>600</v>
       </c>
       <c r="E35" s="3">
+        <v>800</v>
+      </c>
+      <c r="F35" s="3">
+        <v>600</v>
+      </c>
+      <c r="G35" s="3">
         <v>1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1876,43 +2033,49 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1925,8 +2088,14 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1943,8 +2112,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1961,38 +2132,40 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
+        <v>700</v>
+      </c>
+      <c r="F41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1000</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2005,8 +2178,14 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2049,8 +2228,14 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2093,8 +2278,14 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2137,38 +2328,44 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2181,38 +2378,44 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>200</v>
+      </c>
+      <c r="E46" s="3">
         <v>800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
+        <v>800</v>
+      </c>
+      <c r="G46" s="3">
         <v>500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1800</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2225,38 +2428,44 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>69400</v>
+      </c>
+      <c r="F47" s="3">
         <v>67900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>66900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>232400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>229900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>228100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>227000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>226700</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2269,8 +2478,14 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2313,8 +2528,14 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2357,8 +2578,14 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2401,8 +2628,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2445,8 +2678,14 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2489,8 +2728,14 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2533,38 +2778,44 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>70200</v>
+      </c>
+      <c r="F54" s="3">
         <v>68800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>67400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>233000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>230800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>229200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>228300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>228600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2577,8 +2828,14 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2595,8 +2852,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2613,37 +2872,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="E57" s="3">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="F57" s="3">
         <v>2400</v>
       </c>
       <c r="G57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
+      <c r="L57" s="3">
+        <v>0</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
@@ -2657,25 +2918,31 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F58" s="3">
         <v>1500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>600</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2683,14 +2950,14 @@
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2701,8 +2968,14 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2713,10 +2986,10 @@
         <v>200</v>
       </c>
       <c r="F59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H59" s="3">
         <v>300</v>
@@ -2725,14 +2998,14 @@
         <v>300</v>
       </c>
       <c r="J59" s="3">
+        <v>300</v>
+      </c>
+      <c r="K59" s="3">
+        <v>300</v>
+      </c>
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2745,38 +3018,44 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F60" s="3">
         <v>4100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2789,8 +3068,14 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2833,8 +3118,14 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2859,11 +3150,11 @@
       <c r="J62" s="3">
         <v>8100</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="K62" s="3">
+        <v>8100</v>
+      </c>
+      <c r="L62" s="3">
+        <v>8100</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
@@ -2877,8 +3168,14 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2921,8 +3218,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2965,8 +3268,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3009,38 +3318,44 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F66" s="3">
         <v>12200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>11400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>10800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>10400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>9500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>8700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>8800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3053,8 +3368,14 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3071,8 +3392,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3115,8 +3438,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3159,8 +3488,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3203,8 +3538,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3247,38 +3588,44 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-11400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-11000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-10200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-9500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-8400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-7400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-7000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3291,8 +3638,14 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3335,8 +3688,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3379,8 +3738,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3423,37 +3788,43 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>57400</v>
+      </c>
+      <c r="F76" s="3">
         <v>56600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>56000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>222200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>220400</v>
-      </c>
-      <c r="H76" s="3">
-        <v>219700</v>
-      </c>
-      <c r="I76" s="3">
-        <v>219600</v>
       </c>
       <c r="J76" s="3">
         <v>219700</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
+      <c r="K76" s="3">
+        <v>219600</v>
+      </c>
+      <c r="L76" s="3">
+        <v>219700</v>
       </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
@@ -3467,8 +3838,14 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3511,43 +3888,49 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3560,8 +3943,14 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3569,29 +3958,29 @@
         <v>600</v>
       </c>
       <c r="E81" s="3">
+        <v>800</v>
+      </c>
+      <c r="F81" s="3">
+        <v>600</v>
+      </c>
+      <c r="G81" s="3">
         <v>1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3604,8 +3993,14 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3622,8 +4017,10 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3666,8 +4063,14 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3710,8 +4113,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3754,8 +4163,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3798,8 +4213,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3842,8 +4263,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3886,8 +4313,14 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3898,26 +4331,26 @@
         <v>-200</v>
       </c>
       <c r="F89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="G89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="H89" s="3">
         <v>-100</v>
       </c>
       <c r="I89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3930,8 +4363,14 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3948,8 +4387,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3992,8 +4433,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4036,8 +4483,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4080,23 +4533,29 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>167400</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -4104,14 +4563,14 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-226700</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4124,8 +4583,14 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4142,8 +4607,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4186,8 +4653,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4230,8 +4703,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4274,8 +4753,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4318,38 +4803,44 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
+        <v>800</v>
+      </c>
+      <c r="G100" s="3">
         <v>-167300</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>228500</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4362,8 +4853,14 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4406,19 +4903,25 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>100</v>
+      </c>
+      <c r="F102" s="3">
         <v>500</v>
-      </c>
-      <c r="E102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-100</v>
       </c>
       <c r="G102" s="3">
         <v>-100</v>
@@ -4427,17 +4930,17 @@
         <v>-100</v>
       </c>
       <c r="I102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4448,6 +4951,12 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VMCA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VMCA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
   <si>
     <t>VMCA</t>
   </si>
@@ -656,67 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -732,8 +733,11 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -782,8 +786,11 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -832,8 +839,11 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -882,8 +892,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,8 +915,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -952,8 +966,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1002,8 +1019,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1052,8 +1072,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1102,8 +1125,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1119,41 +1145,42 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>500</v>
+      </c>
+      <c r="E17" s="3">
         <v>300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>100</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1169,8 +1196,11 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1178,32 +1208,32 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1219,8 +1249,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1239,8 +1272,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1248,31 +1282,31 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F20" s="3">
         <v>900</v>
       </c>
       <c r="G20" s="3">
+        <v>900</v>
+      </c>
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1289,8 +1323,11 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1298,20 +1335,20 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>600</v>
+      </c>
+      <c r="F21" s="3">
         <v>800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1800</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1339,8 +1376,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1389,40 +1429,43 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>200</v>
+      </c>
+      <c r="E23" s="3">
         <v>600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>100</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-100</v>
       </c>
       <c r="L23" s="3">
         <v>-100</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
+      <c r="M23" s="3">
+        <v>-100</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
@@ -1439,8 +1482,11 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1489,8 +1535,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1539,40 +1588,43 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>200</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>100</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-100</v>
       </c>
       <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
+      <c r="M26" s="3">
+        <v>-100</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
@@ -1589,40 +1641,43 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>200</v>
+      </c>
+      <c r="E27" s="3">
         <v>600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>100</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-100</v>
       </c>
       <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
+      <c r="M27" s="3">
+        <v>-100</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
@@ -1639,8 +1694,11 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1689,8 +1747,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1739,8 +1800,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1789,8 +1853,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1839,8 +1906,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1848,31 +1918,31 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="F32" s="3">
         <v>-900</v>
       </c>
       <c r="G32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1889,40 +1959,43 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>200</v>
+      </c>
+      <c r="E33" s="3">
         <v>600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>100</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-100</v>
       </c>
       <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
+      <c r="M33" s="3">
+        <v>-100</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
@@ -1939,8 +2012,11 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1989,40 +2065,43 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>200</v>
+      </c>
+      <c r="E35" s="3">
         <v>600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>100</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-100</v>
       </c>
       <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
+      <c r="M35" s="3">
+        <v>-100</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
@@ -2039,46 +2118,49 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2094,8 +2176,11 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2114,8 +2199,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2134,8 +2220,9 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2143,32 +2230,32 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>300</v>
-      </c>
-      <c r="J41" s="3">
-        <v>500</v>
       </c>
       <c r="K41" s="3">
         <v>500</v>
       </c>
       <c r="L41" s="3">
+        <v>500</v>
+      </c>
+      <c r="M41" s="3">
         <v>1000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2184,8 +2271,11 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2234,8 +2324,11 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2284,8 +2377,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2334,8 +2430,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2346,29 +2445,29 @@
         <v>100</v>
       </c>
       <c r="F45" s="3">
+        <v>100</v>
+      </c>
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>500</v>
       </c>
       <c r="I45" s="3">
         <v>500</v>
       </c>
       <c r="J45" s="3">
+        <v>500</v>
+      </c>
+      <c r="K45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2384,41 +2483,44 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>100</v>
+      </c>
+      <c r="E46" s="3">
         <v>200</v>
-      </c>
-      <c r="E46" s="3">
-        <v>800</v>
       </c>
       <c r="F46" s="3">
         <v>800</v>
       </c>
       <c r="G46" s="3">
+        <v>800</v>
+      </c>
+      <c r="H46" s="3">
         <v>500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1800</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,41 +2536,44 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E47" s="3">
         <v>70700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>69400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>67900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>66900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>232400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>229900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>228100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>227000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>226700</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2484,8 +2589,11 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2534,8 +2642,11 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2584,8 +2695,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2634,8 +2748,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2684,8 +2801,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2734,8 +2854,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2784,41 +2907,44 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E54" s="3">
         <v>70800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>70200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>68800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>67400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>233000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>230800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>229200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>228300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>228600</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2834,8 +2960,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2854,8 +2983,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2874,40 +3004,41 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
+      <c r="M57" s="3">
+        <v>0</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
@@ -2924,28 +3055,31 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2300</v>
+        <v>2600</v>
       </c>
       <c r="E58" s="3">
         <v>2300</v>
       </c>
       <c r="F58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G58" s="3">
         <v>1500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>600</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -2956,11 +3090,11 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -2974,13 +3108,16 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
         <v>200</v>
@@ -2992,7 +3129,7 @@
         <v>200</v>
       </c>
       <c r="H59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I59" s="3">
         <v>300</v>
@@ -3004,11 +3141,11 @@
         <v>300</v>
       </c>
       <c r="L59" s="3">
+        <v>300</v>
+      </c>
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,41 +3161,44 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E60" s="3">
         <v>4800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3074,8 +3214,11 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3124,8 +3267,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3156,8 +3302,8 @@
       <c r="L62" s="3">
         <v>8100</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3">
+        <v>8100</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -3174,8 +3320,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3224,8 +3373,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3274,8 +3426,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3324,41 +3479,44 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E66" s="3">
         <v>12900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8800</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3374,8 +3532,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3394,8 +3555,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3444,8 +3606,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3494,8 +3659,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3544,8 +3712,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3594,41 +3765,44 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-12600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-9500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3644,8 +3818,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3694,8 +3871,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3744,8 +3924,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3794,41 +3977,44 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E76" s="3">
         <v>58000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>57400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>56600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>56000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>222200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>220400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>219700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>219600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>219700</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,8 +4030,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3894,46 +4083,49 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3949,40 +4141,43 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>200</v>
+      </c>
+      <c r="E81" s="3">
         <v>600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>100</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-100</v>
       </c>
       <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
+      <c r="M81" s="3">
+        <v>-100</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
@@ -3999,8 +4194,11 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4019,8 +4217,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4069,8 +4268,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4119,8 +4321,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4169,8 +4374,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4219,8 +4427,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4269,8 +4480,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4319,13 +4533,16 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="E89" s="3">
         <v>-200</v>
@@ -4337,7 +4554,7 @@
         <v>-200</v>
       </c>
       <c r="H89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="I89" s="3">
         <v>-100</v>
@@ -4346,14 +4563,14 @@
         <v>-100</v>
       </c>
       <c r="K89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4369,8 +4586,11 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4389,8 +4609,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4439,8 +4660,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4489,8 +4713,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4539,26 +4766,29 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>167400</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
@@ -4569,11 +4799,11 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-226700</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4589,8 +4819,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4609,8 +4842,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4659,8 +4893,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4709,8 +4946,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4759,8 +4999,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4809,26 +5052,29 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="3">
-        <v>800</v>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
         <v>800</v>
       </c>
       <c r="G100" s="3">
+        <v>800</v>
+      </c>
+      <c r="H100" s="3">
         <v>-167300</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -4836,14 +5082,14 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>228500</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4859,8 +5105,11 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4909,22 +5158,25 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>500</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-100</v>
       </c>
       <c r="H102" s="3">
         <v>-100</v>
@@ -4936,14 +5188,14 @@
         <v>-100</v>
       </c>
       <c r="K102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>800</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4957,6 +5209,9 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
